--- a/data/trans_bre/P2A_enfcro_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 16,48</t>
+          <t>-1,22; 16,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,11; 24,21</t>
+          <t>8,99; 24,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 19,54</t>
+          <t>3,84; 19,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 16,25</t>
+          <t>-0,14; 16,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 44,6</t>
+          <t>-2,81; 44,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,2; 43,34</t>
+          <t>14,93; 45,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 40,33</t>
+          <t>6,63; 39,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 30,51</t>
+          <t>-0,26; 31,49</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,38; 25,83</t>
+          <t>13,3; 26,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,6; 23,14</t>
+          <t>10,92; 23,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 19,95</t>
+          <t>7,91; 19,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 10,98</t>
+          <t>-1,83; 11,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,78; 70,34</t>
+          <t>30,09; 71,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,92; 48,97</t>
+          <t>20,16; 49,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 38,06</t>
+          <t>13,53; 38,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 36,72</t>
+          <t>-4,98; 39,83</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,27; 31,32</t>
+          <t>16,22; 31,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 15,92</t>
+          <t>0,48; 15,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 16,04</t>
+          <t>2,2; 17,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 11,47</t>
+          <t>-2,47; 11,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,47; 79,79</t>
+          <t>33,98; 80,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 29,57</t>
+          <t>0,78; 28,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 33,74</t>
+          <t>3,94; 35,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 32,95</t>
+          <t>-5,67; 30,66</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,35; 25,86</t>
+          <t>11,33; 25,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 20,58</t>
+          <t>6,22; 20,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,08; 20,97</t>
+          <t>6,6; 20,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 8,99</t>
+          <t>-18,38; 9,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,18; 54,62</t>
+          <t>21,03; 54,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,35; 39,59</t>
+          <t>9,88; 37,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,9; 40,71</t>
+          <t>10,92; 40,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 22,62</t>
+          <t>-41,97; 25,66</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 23,52</t>
+          <t>3,75; 22,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,25; 35,16</t>
+          <t>17,15; 34,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,86</t>
+          <t>0,25; 17,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 3,67</t>
+          <t>-6,85; 4,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,11; 62,24</t>
+          <t>8,07; 60,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,69; 75,0</t>
+          <t>29,11; 72,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 39,22</t>
+          <t>0,59; 39,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-51,05; 46,22</t>
+          <t>-53,06; 54,69</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,09; 22,32</t>
+          <t>5,25; 22,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,63; 22,33</t>
+          <t>6,78; 22,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,26; 20,11</t>
+          <t>3,27; 21,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 9,45</t>
+          <t>-5,35; 9,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,37; 49,95</t>
+          <t>9,18; 49,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,84; 38,69</t>
+          <t>9,83; 39,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,07; 50,8</t>
+          <t>6,19; 52,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 21,81</t>
+          <t>-10,17; 19,64</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,37; 23,06</t>
+          <t>11,62; 22,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 15,66</t>
+          <t>4,53; 15,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,02; 16,93</t>
+          <t>5,69; 17,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,28; 48,64</t>
+          <t>2,94; 51,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,28; 60,86</t>
+          <t>26,32; 58,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,5; 29,46</t>
+          <t>7,74; 28,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,98; 43,46</t>
+          <t>12,44; 44,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,11; 279,41</t>
+          <t>12,17; 278,76</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,24; 17,48</t>
+          <t>7,67; 17,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,88; 17,55</t>
+          <t>7,63; 17,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,49; 15,57</t>
+          <t>5,33; 15,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,93; 32,73</t>
+          <t>10,15; 31,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,72; 40,37</t>
+          <t>16,03; 39,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,04; 43,6</t>
+          <t>16,73; 43,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,94; 34,6</t>
+          <t>10,61; 33,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,77; 323,41</t>
+          <t>33,55; 303,78</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,69; 18,43</t>
+          <t>13,69; 18,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,54; 16,1</t>
+          <t>11,39; 16,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,3; 13,95</t>
+          <t>9,39; 13,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,45; 22,02</t>
+          <t>4,72; 23,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,96; 42,9</t>
+          <t>29,99; 43,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,88; 30,53</t>
+          <t>20,51; 30,79</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,12; 28,53</t>
+          <t>18,25; 29,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,84; 78,75</t>
+          <t>14,02; 81,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,72</t>
+          <t>8,71</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 16,51</t>
+          <t>-0,51; 16,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,99; 24,65</t>
+          <t>9,14; 24,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 19,05</t>
+          <t>3,11; 19,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 16,92</t>
+          <t>0,97; 15,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 44,41</t>
+          <t>-1,89; 44,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,93; 45,9</t>
+          <t>14,32; 44,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 39,15</t>
+          <t>5,44; 40,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 31,49</t>
+          <t>0,89; 30,65</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>4,8</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,3; 26,25</t>
+          <t>13,24; 26,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,92; 23,66</t>
+          <t>11,79; 24,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,91; 19,97</t>
+          <t>7,89; 20,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 11,36</t>
+          <t>-1,69; 10,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,09; 71,39</t>
+          <t>30,73; 72,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,16; 49,37</t>
+          <t>21,58; 50,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,53; 38,38</t>
+          <t>13,24; 38,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 39,83</t>
+          <t>-4,43; 38,21</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,43</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,22; 31,0</t>
+          <t>16,15; 31,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 15,83</t>
+          <t>0,9; 15,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 17,08</t>
+          <t>1,7; 16,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 11,35</t>
+          <t>-2,36; 11,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,98; 80,15</t>
+          <t>33,81; 79,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 28,85</t>
+          <t>1,33; 28,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 35,63</t>
+          <t>3,07; 36,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 30,66</t>
+          <t>-5,2; 33,6</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,3</t>
+          <t>8,52</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-5,62%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 25,11</t>
+          <t>10,95; 25,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 20,17</t>
+          <t>5,76; 19,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,6; 20,73</t>
+          <t>7,28; 21,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 9,85</t>
+          <t>0,19; 17,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,03; 54,08</t>
+          <t>20,16; 55,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,88; 37,83</t>
+          <t>9,5; 38,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,92; 40,41</t>
+          <t>12,51; 42,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,97; 25,66</t>
+          <t>0,33; 49,14</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-4,91%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 22,8</t>
+          <t>3,71; 23,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,15; 34,66</t>
+          <t>17,87; 36,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 17,98</t>
+          <t>-0,84; 18,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 4,45</t>
+          <t>-2,5; 6,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,07; 60,53</t>
+          <t>8,14; 59,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,11; 72,5</t>
+          <t>29,82; 77,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 39,81</t>
+          <t>-1,59; 39,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-53,06; 54,69</t>
+          <t>-21,06; 95,41</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,25; 22,22</t>
+          <t>4,49; 22,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,78; 22,68</t>
+          <t>7,38; 22,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,27; 21,14</t>
+          <t>2,43; 20,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 9,06</t>
+          <t>-6,56; 8,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,18; 49,53</t>
+          <t>7,91; 47,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,83; 39,06</t>
+          <t>11,05; 39,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,19; 52,15</t>
+          <t>4,95; 49,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 19,64</t>
+          <t>-12,33; 18,69</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22,56</t>
+          <t>6,2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>102,52%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,62; 22,78</t>
+          <t>11,3; 22,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,53; 15,45</t>
+          <t>4,33; 15,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 17,42</t>
+          <t>5,65; 17,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 51,77</t>
+          <t>1,67; 10,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,32; 58,8</t>
+          <t>25,89; 58,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,74; 28,72</t>
+          <t>7,07; 28,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,44; 44,22</t>
+          <t>12,55; 44,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,17; 278,76</t>
+          <t>6,94; 57,54</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19,41</t>
+          <t>12,11</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,67; 17,22</t>
+          <t>6,88; 16,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,63; 17,51</t>
+          <t>8,17; 17,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,33; 15,34</t>
+          <t>5,79; 16,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,15; 31,55</t>
+          <t>7,58; 16,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,03; 39,92</t>
+          <t>14,08; 38,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,73; 43,35</t>
+          <t>17,56; 43,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,61; 33,69</t>
+          <t>11,36; 35,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>33,55; 303,78</t>
+          <t>24,16; 61,85</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10,22</t>
+          <t>6,81</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,69; 18,36</t>
+          <t>13,65; 18,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,39; 16,26</t>
+          <t>11,34; 16,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,39; 13,98</t>
+          <t>9,13; 13,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,72; 23,1</t>
+          <t>4,73; 9,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,99; 43,08</t>
+          <t>29,81; 42,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,51; 30,79</t>
+          <t>20,6; 30,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,25; 29,04</t>
+          <t>17,98; 29,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,02; 81,34</t>
+          <t>13,9; 28,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Población que convive con personas con enfermedades crónicas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
